--- a/artfynd/A 13453-2024 artfynd.xlsx
+++ b/artfynd/A 13453-2024 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121692586</v>
+        <v>121692585</v>
       </c>
       <c r="B3" t="n">
-        <v>79234</v>
+        <v>5173</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,25 +812,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -840,7 +840,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,13 +854,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516081</v>
+        <v>516079</v>
       </c>
       <c r="R3" t="n">
-        <v>6585590</v>
+        <v>6585587</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +889,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +899,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,10 +930,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121692587</v>
+        <v>121692589</v>
       </c>
       <c r="B4" t="n">
-        <v>8425</v>
+        <v>90728</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,40 +942,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516166</v>
+        <v>516189</v>
       </c>
       <c r="R4" t="n">
-        <v>6585544</v>
+        <v>6585528</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1055,7 +1055,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121692590</v>
+        <v>121692587</v>
       </c>
       <c r="B5" t="n">
         <v>8425</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1109,10 +1109,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516204</v>
+        <v>516166</v>
       </c>
       <c r="R5" t="n">
-        <v>6585475</v>
+        <v>6585544</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1315,10 +1315,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121692585</v>
+        <v>121692592</v>
       </c>
       <c r="B7" t="n">
-        <v>5173</v>
+        <v>8425</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1331,21 +1331,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1369,13 +1369,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516079</v>
+        <v>516205</v>
       </c>
       <c r="R7" t="n">
-        <v>6585587</v>
+        <v>6585468</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1445,10 +1445,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121692901</v>
+        <v>121692583</v>
       </c>
       <c r="B8" t="n">
-        <v>58034</v>
+        <v>56569</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1461,21 +1461,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103044</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1494,13 +1494,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516180</v>
+        <v>516082</v>
       </c>
       <c r="R8" t="n">
-        <v>6585577</v>
+        <v>6585587</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1524,22 +1524,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ola Erlandsson</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1570,10 +1570,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121692581</v>
+        <v>121692586</v>
       </c>
       <c r="B9" t="n">
-        <v>8425</v>
+        <v>79234</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1582,25 +1582,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1610,12 +1610,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1624,10 +1619,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516114</v>
+        <v>516081</v>
       </c>
       <c r="R9" t="n">
-        <v>6585510</v>
+        <v>6585590</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1659,7 +1654,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1669,7 +1664,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1830,10 +1825,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121692589</v>
+        <v>121692581</v>
       </c>
       <c r="B11" t="n">
-        <v>90728</v>
+        <v>8425</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1842,25 +1837,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1870,7 +1865,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516189</v>
+        <v>516114</v>
       </c>
       <c r="R11" t="n">
-        <v>6585528</v>
+        <v>6585510</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2080,10 +2080,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121692583</v>
+        <v>121692590</v>
       </c>
       <c r="B13" t="n">
-        <v>56569</v>
+        <v>8425</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2096,21 +2096,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>106554</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2118,9 +2118,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2129,13 +2134,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516082</v>
+        <v>516204</v>
       </c>
       <c r="R13" t="n">
-        <v>6585587</v>
+        <v>6585475</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2164,7 +2169,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2174,7 +2179,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2205,10 +2210,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121692592</v>
+        <v>121692901</v>
       </c>
       <c r="B14" t="n">
-        <v>8425</v>
+        <v>58034</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2221,21 +2226,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106554</v>
+        <v>103044</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2243,14 +2248,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2259,13 +2259,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516205</v>
+        <v>516180</v>
       </c>
       <c r="R14" t="n">
-        <v>6585468</v>
+        <v>6585577</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2289,22 +2289,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Ola Erlandsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">

--- a/artfynd/A 13453-2024 artfynd.xlsx
+++ b/artfynd/A 13453-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121692588</v>
+        <v>121692585</v>
       </c>
       <c r="B2" t="n">
-        <v>90693</v>
+        <v>5173</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +715,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +729,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>516188</v>
+        <v>516079</v>
       </c>
       <c r="R2" t="n">
-        <v>6585531</v>
+        <v>6585587</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121692585</v>
+        <v>121692592</v>
       </c>
       <c r="B3" t="n">
-        <v>5173</v>
+        <v>8425</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,21 +821,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -854,13 +859,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516079</v>
+        <v>516205</v>
       </c>
       <c r="R3" t="n">
-        <v>6585587</v>
+        <v>6585468</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -899,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121692589</v>
+        <v>121692583</v>
       </c>
       <c r="B4" t="n">
-        <v>90728</v>
+        <v>56569</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -942,25 +947,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -968,9 +973,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -979,13 +984,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516189</v>
+        <v>516082</v>
       </c>
       <c r="R4" t="n">
-        <v>6585528</v>
+        <v>6585587</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1014,7 +1019,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1024,7 +1029,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1055,10 +1060,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121692587</v>
+        <v>121690948</v>
       </c>
       <c r="B5" t="n">
-        <v>8425</v>
+        <v>57726</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1071,36 +1076,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ex.</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1109,10 +1109,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516166</v>
+        <v>516203</v>
       </c>
       <c r="R5" t="n">
-        <v>6585544</v>
+        <v>6585542</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1139,22 +1139,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Indre Cepukaite</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1185,10 +1185,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121692582</v>
+        <v>121692584</v>
       </c>
       <c r="B6" t="n">
-        <v>8425</v>
+        <v>5193</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516064</v>
+        <v>516080</v>
       </c>
       <c r="R6" t="n">
-        <v>6585564</v>
+        <v>6585588</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1315,7 +1315,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121692592</v>
+        <v>121692581</v>
       </c>
       <c r="B7" t="n">
         <v>8425</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516205</v>
+        <v>516114</v>
       </c>
       <c r="R7" t="n">
-        <v>6585468</v>
+        <v>6585510</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1445,10 +1445,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121692583</v>
+        <v>121692590</v>
       </c>
       <c r="B8" t="n">
-        <v>56569</v>
+        <v>8425</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1461,21 +1461,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1483,9 +1483,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1494,13 +1499,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516082</v>
+        <v>516204</v>
       </c>
       <c r="R8" t="n">
-        <v>6585587</v>
+        <v>6585475</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1529,7 +1534,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1539,7 +1544,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1570,10 +1575,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121692586</v>
+        <v>121692588</v>
       </c>
       <c r="B9" t="n">
-        <v>79234</v>
+        <v>90693</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1582,25 +1587,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1610,7 +1615,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1619,10 +1624,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516081</v>
+        <v>516188</v>
       </c>
       <c r="R9" t="n">
-        <v>6585590</v>
+        <v>6585531</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1654,7 +1659,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1664,7 +1669,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1695,10 +1700,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121692584</v>
+        <v>121692587</v>
       </c>
       <c r="B10" t="n">
-        <v>5193</v>
+        <v>8425</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1711,26 +1716,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1749,10 +1754,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516080</v>
+        <v>516166</v>
       </c>
       <c r="R10" t="n">
-        <v>6585588</v>
+        <v>6585544</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1784,7 +1789,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1794,7 +1799,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1825,10 +1830,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121692581</v>
+        <v>121692901</v>
       </c>
       <c r="B11" t="n">
-        <v>8425</v>
+        <v>58034</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1841,21 +1846,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106554</v>
+        <v>103044</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1863,14 +1868,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1879,13 +1879,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516114</v>
+        <v>516180</v>
       </c>
       <c r="R11" t="n">
-        <v>6585510</v>
+        <v>6585577</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1909,22 +1909,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Ola Erlandsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1955,10 +1955,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121690948</v>
+        <v>121692582</v>
       </c>
       <c r="B12" t="n">
-        <v>57726</v>
+        <v>8425</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1971,21 +1971,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>106554</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1993,9 +1993,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2004,10 +2009,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>516203</v>
+        <v>516064</v>
       </c>
       <c r="R12" t="n">
-        <v>6585542</v>
+        <v>6585564</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -2034,22 +2039,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>07:23</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>07:23</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2069,7 +2074,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Indre Cepukaite</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2080,10 +2085,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121692590</v>
+        <v>121692586</v>
       </c>
       <c r="B13" t="n">
-        <v>8425</v>
+        <v>79234</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2092,25 +2097,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106554</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2120,12 +2125,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516204</v>
+        <v>516081</v>
       </c>
       <c r="R13" t="n">
-        <v>6585475</v>
+        <v>6585590</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2210,10 +2210,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121692901</v>
+        <v>121692589</v>
       </c>
       <c r="B14" t="n">
-        <v>58034</v>
+        <v>90728</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2222,25 +2222,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103044</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2248,9 +2248,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2259,13 +2259,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516180</v>
+        <v>516189</v>
       </c>
       <c r="R14" t="n">
-        <v>6585577</v>
+        <v>6585528</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2289,22 +2289,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ola Erlandsson</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">

--- a/artfynd/A 13453-2024 artfynd.xlsx
+++ b/artfynd/A 13453-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121692585</v>
+        <v>121692586</v>
       </c>
       <c r="B2" t="n">
-        <v>5173</v>
+        <v>79234</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,12 +715,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>516079</v>
+        <v>516081</v>
       </c>
       <c r="R2" t="n">
-        <v>6585587</v>
+        <v>6585590</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121692592</v>
+        <v>121692589</v>
       </c>
       <c r="B3" t="n">
-        <v>8425</v>
+        <v>90728</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,25 +812,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -845,12 +840,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516205</v>
+        <v>516189</v>
       </c>
       <c r="R3" t="n">
-        <v>6585468</v>
+        <v>6585528</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -894,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121692583</v>
+        <v>121692588</v>
       </c>
       <c r="B4" t="n">
-        <v>56569</v>
+        <v>90693</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,21 +941,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -973,9 +963,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -984,13 +974,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516082</v>
+        <v>516188</v>
       </c>
       <c r="R4" t="n">
-        <v>6585587</v>
+        <v>6585531</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1019,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1029,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1060,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121690948</v>
+        <v>121692590</v>
       </c>
       <c r="B5" t="n">
-        <v>57726</v>
+        <v>8425</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1076,21 +1066,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1098,9 +1088,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1109,10 +1104,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516203</v>
+        <v>516204</v>
       </c>
       <c r="R5" t="n">
-        <v>6585542</v>
+        <v>6585475</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1139,22 +1134,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:23</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:23</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1174,7 +1169,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Indre Cepukaite</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1185,10 +1180,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121692584</v>
+        <v>121690948</v>
       </c>
       <c r="B6" t="n">
-        <v>5193</v>
+        <v>57726</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1201,16 +1196,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1223,14 +1218,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1239,10 +1229,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516080</v>
+        <v>516203</v>
       </c>
       <c r="R6" t="n">
-        <v>6585588</v>
+        <v>6585542</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1269,22 +1259,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1304,7 +1294,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Indre Cepukaite</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1445,10 +1435,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121692590</v>
+        <v>121692585</v>
       </c>
       <c r="B8" t="n">
-        <v>8425</v>
+        <v>5173</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1461,21 +1451,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1499,13 +1489,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516204</v>
+        <v>516079</v>
       </c>
       <c r="R8" t="n">
-        <v>6585475</v>
+        <v>6585587</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1534,7 +1524,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1544,7 +1534,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1575,10 +1565,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121692588</v>
+        <v>121692582</v>
       </c>
       <c r="B9" t="n">
-        <v>90693</v>
+        <v>8425</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1591,21 +1581,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1615,7 +1605,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1624,10 +1619,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516188</v>
+        <v>516064</v>
       </c>
       <c r="R9" t="n">
-        <v>6585531</v>
+        <v>6585564</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1659,7 +1654,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1669,7 +1664,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1700,10 +1695,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121692587</v>
+        <v>121692583</v>
       </c>
       <c r="B10" t="n">
-        <v>8425</v>
+        <v>56569</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1716,36 +1711,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106554</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>ex.</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1754,13 +1744,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516166</v>
+        <v>516082</v>
       </c>
       <c r="R10" t="n">
-        <v>6585544</v>
+        <v>6585587</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1789,7 +1779,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1799,7 +1789,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1830,10 +1820,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121692901</v>
+        <v>121692592</v>
       </c>
       <c r="B11" t="n">
-        <v>58034</v>
+        <v>8425</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1846,21 +1836,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103044</v>
+        <v>106554</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1868,9 +1858,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1879,13 +1874,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516180</v>
+        <v>516205</v>
       </c>
       <c r="R11" t="n">
-        <v>6585577</v>
+        <v>6585468</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1909,22 +1904,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1944,7 +1939,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ola Erlandsson</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1955,10 +1950,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121692582</v>
+        <v>121692901</v>
       </c>
       <c r="B12" t="n">
-        <v>8425</v>
+        <v>58034</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1971,21 +1966,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106554</v>
+        <v>103044</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1993,14 +1988,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2009,13 +1999,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>516064</v>
+        <v>516180</v>
       </c>
       <c r="R12" t="n">
-        <v>6585564</v>
+        <v>6585577</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2039,22 +2029,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2074,7 +2064,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Ola Erlandsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2085,10 +2075,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121692586</v>
+        <v>121692584</v>
       </c>
       <c r="B13" t="n">
-        <v>79234</v>
+        <v>5193</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2097,25 +2087,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>105930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2125,7 +2115,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2134,10 +2129,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516081</v>
+        <v>516080</v>
       </c>
       <c r="R13" t="n">
-        <v>6585590</v>
+        <v>6585588</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2169,7 +2164,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2179,7 +2174,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2210,10 +2205,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121692589</v>
+        <v>121692587</v>
       </c>
       <c r="B14" t="n">
-        <v>90728</v>
+        <v>8425</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2222,35 +2217,40 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516189</v>
+        <v>516166</v>
       </c>
       <c r="R14" t="n">
-        <v>6585528</v>
+        <v>6585544</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 13453-2024 artfynd.xlsx
+++ b/artfynd/A 13453-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121692586</v>
+        <v>121692592</v>
       </c>
       <c r="B2" t="n">
-        <v>79234</v>
+        <v>8425</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +715,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>516081</v>
+        <v>516205</v>
       </c>
       <c r="R2" t="n">
-        <v>6585590</v>
+        <v>6585468</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121692589</v>
+        <v>121692581</v>
       </c>
       <c r="B3" t="n">
-        <v>90728</v>
+        <v>8425</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,25 +817,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -840,7 +845,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516189</v>
+        <v>516114</v>
       </c>
       <c r="R3" t="n">
-        <v>6585528</v>
+        <v>6585510</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -884,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121692588</v>
+        <v>121692590</v>
       </c>
       <c r="B4" t="n">
-        <v>90693</v>
+        <v>8425</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,21 +951,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -965,7 +975,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -974,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516188</v>
+        <v>516204</v>
       </c>
       <c r="R4" t="n">
-        <v>6585531</v>
+        <v>6585475</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1009,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1034,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121692590</v>
+        <v>121692585</v>
       </c>
       <c r="B5" t="n">
-        <v>8425</v>
+        <v>5173</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,21 +1081,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1104,13 +1119,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516204</v>
+        <v>516079</v>
       </c>
       <c r="R5" t="n">
-        <v>6585475</v>
+        <v>6585587</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1139,7 +1154,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1149,7 +1164,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1305,10 +1320,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121692581</v>
+        <v>121692584</v>
       </c>
       <c r="B7" t="n">
-        <v>8425</v>
+        <v>5193</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1321,21 +1336,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1359,10 +1374,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516114</v>
+        <v>516080</v>
       </c>
       <c r="R7" t="n">
-        <v>6585510</v>
+        <v>6585588</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1394,7 +1409,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1404,7 +1419,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1435,10 +1450,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121692585</v>
+        <v>121692582</v>
       </c>
       <c r="B8" t="n">
-        <v>5173</v>
+        <v>8425</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1451,21 +1466,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1489,13 +1504,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516079</v>
+        <v>516064</v>
       </c>
       <c r="R8" t="n">
-        <v>6585587</v>
+        <v>6585564</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1524,7 +1539,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1534,7 +1549,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1565,10 +1580,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121692582</v>
+        <v>121692589</v>
       </c>
       <c r="B9" t="n">
-        <v>8425</v>
+        <v>90728</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1577,25 +1592,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1605,12 +1620,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1619,10 +1629,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516064</v>
+        <v>516189</v>
       </c>
       <c r="R9" t="n">
-        <v>6585564</v>
+        <v>6585528</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1654,7 +1664,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1664,7 +1674,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1695,10 +1705,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121692583</v>
+        <v>121692588</v>
       </c>
       <c r="B10" t="n">
-        <v>56569</v>
+        <v>90693</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1711,21 +1721,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1733,9 +1743,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1744,13 +1754,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516082</v>
+        <v>516188</v>
       </c>
       <c r="R10" t="n">
-        <v>6585587</v>
+        <v>6585531</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1779,7 +1789,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1789,7 +1799,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1820,10 +1830,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121692592</v>
+        <v>121692583</v>
       </c>
       <c r="B11" t="n">
-        <v>8425</v>
+        <v>56569</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1836,21 +1846,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106554</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1858,14 +1868,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1874,13 +1879,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516205</v>
+        <v>516082</v>
       </c>
       <c r="R11" t="n">
-        <v>6585468</v>
+        <v>6585587</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1909,7 +1914,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1919,7 +1924,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1950,10 +1955,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121692901</v>
+        <v>121692586</v>
       </c>
       <c r="B12" t="n">
-        <v>58034</v>
+        <v>79234</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1962,25 +1967,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103044</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1988,9 +1993,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1999,13 +2004,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>516180</v>
+        <v>516081</v>
       </c>
       <c r="R12" t="n">
-        <v>6585577</v>
+        <v>6585590</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2029,22 +2034,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2064,7 +2069,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ola Erlandsson</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2075,10 +2080,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121692584</v>
+        <v>121692587</v>
       </c>
       <c r="B13" t="n">
-        <v>5193</v>
+        <v>8425</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2091,26 +2096,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2129,10 +2134,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516080</v>
+        <v>516166</v>
       </c>
       <c r="R13" t="n">
-        <v>6585588</v>
+        <v>6585544</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2164,7 +2169,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2174,7 +2179,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2205,10 +2210,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121692587</v>
+        <v>121692901</v>
       </c>
       <c r="B14" t="n">
-        <v>8425</v>
+        <v>58034</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2221,36 +2226,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106554</v>
+        <v>103044</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>ex.</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2259,13 +2259,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516166</v>
+        <v>516180</v>
       </c>
       <c r="R14" t="n">
-        <v>6585544</v>
+        <v>6585577</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2289,22 +2289,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Ola Erlandsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">

--- a/artfynd/A 13453-2024 artfynd.xlsx
+++ b/artfynd/A 13453-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121692592</v>
+        <v>121692588</v>
       </c>
       <c r="B2" t="n">
-        <v>8425</v>
+        <v>90693</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,12 +715,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>516205</v>
+        <v>516188</v>
       </c>
       <c r="R2" t="n">
-        <v>6585468</v>
+        <v>6585531</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -764,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121692581</v>
+        <v>121690948</v>
       </c>
       <c r="B3" t="n">
-        <v>8425</v>
+        <v>57726</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,21 +816,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -843,14 +838,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516114</v>
+        <v>516203</v>
       </c>
       <c r="R3" t="n">
-        <v>6585510</v>
+        <v>6585542</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -889,22 +879,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,7 +914,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Indre Cepukaite</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1065,10 +1055,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121692585</v>
+        <v>121692586</v>
       </c>
       <c r="B5" t="n">
-        <v>5173</v>
+        <v>79234</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1077,25 +1067,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1105,12 +1095,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1119,13 +1104,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516079</v>
+        <v>516081</v>
       </c>
       <c r="R5" t="n">
-        <v>6585587</v>
+        <v>6585590</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1154,7 +1139,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1164,7 +1149,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1195,10 +1180,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121690948</v>
+        <v>121692901</v>
       </c>
       <c r="B6" t="n">
-        <v>57726</v>
+        <v>58034</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1211,16 +1196,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1235,7 +1220,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1244,13 +1229,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516203</v>
+        <v>516180</v>
       </c>
       <c r="R6" t="n">
-        <v>6585542</v>
+        <v>6585577</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1274,22 +1259,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:23</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:23</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1309,7 +1294,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Indre Cepukaite</t>
+          <t>Ola Erlandsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1320,10 +1305,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121692584</v>
+        <v>121692583</v>
       </c>
       <c r="B7" t="n">
-        <v>5193</v>
+        <v>56569</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1336,21 +1321,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1358,14 +1343,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1374,13 +1354,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516080</v>
+        <v>516082</v>
       </c>
       <c r="R7" t="n">
-        <v>6585588</v>
+        <v>6585587</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1409,7 +1389,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1419,7 +1399,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1450,10 +1430,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121692582</v>
+        <v>121692585</v>
       </c>
       <c r="B8" t="n">
-        <v>8425</v>
+        <v>5173</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1466,21 +1446,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1504,13 +1484,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516064</v>
+        <v>516079</v>
       </c>
       <c r="R8" t="n">
-        <v>6585564</v>
+        <v>6585587</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1539,7 +1519,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1549,7 +1529,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1580,10 +1560,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121692589</v>
+        <v>121692584</v>
       </c>
       <c r="B9" t="n">
-        <v>90728</v>
+        <v>5193</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1592,25 +1572,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1620,7 +1600,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1629,10 +1614,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516189</v>
+        <v>516080</v>
       </c>
       <c r="R9" t="n">
-        <v>6585528</v>
+        <v>6585588</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1664,7 +1649,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1674,7 +1659,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1705,10 +1690,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121692588</v>
+        <v>121692592</v>
       </c>
       <c r="B10" t="n">
-        <v>90693</v>
+        <v>8425</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1721,21 +1706,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>106554</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1745,7 +1730,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1754,10 +1744,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516188</v>
+        <v>516205</v>
       </c>
       <c r="R10" t="n">
-        <v>6585531</v>
+        <v>6585468</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1789,7 +1779,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1799,7 +1789,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1830,10 +1820,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121692583</v>
+        <v>121692587</v>
       </c>
       <c r="B11" t="n">
-        <v>56569</v>
+        <v>8425</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1846,31 +1836,36 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>106554</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1879,13 +1874,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516082</v>
+        <v>516166</v>
       </c>
       <c r="R11" t="n">
-        <v>6585587</v>
+        <v>6585544</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1914,7 +1909,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1924,7 +1919,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1955,10 +1950,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121692586</v>
+        <v>121692581</v>
       </c>
       <c r="B12" t="n">
-        <v>79234</v>
+        <v>8425</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1967,25 +1962,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>106554</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1995,7 +1990,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>516081</v>
+        <v>516114</v>
       </c>
       <c r="R12" t="n">
-        <v>6585590</v>
+        <v>6585510</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2080,10 +2080,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121692587</v>
+        <v>121692589</v>
       </c>
       <c r="B13" t="n">
-        <v>8425</v>
+        <v>90728</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2092,40 +2092,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2134,10 +2129,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516166</v>
+        <v>516189</v>
       </c>
       <c r="R13" t="n">
-        <v>6585544</v>
+        <v>6585528</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2169,7 +2164,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2179,7 +2174,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2210,10 +2205,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121692901</v>
+        <v>121692582</v>
       </c>
       <c r="B14" t="n">
-        <v>58034</v>
+        <v>8425</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2226,21 +2221,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103044</v>
+        <v>106554</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2248,9 +2243,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2259,13 +2259,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516180</v>
+        <v>516064</v>
       </c>
       <c r="R14" t="n">
-        <v>6585577</v>
+        <v>6585564</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2289,22 +2289,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ola Erlandsson</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">

--- a/artfynd/A 13453-2024 artfynd.xlsx
+++ b/artfynd/A 13453-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121692588</v>
+        <v>121692582</v>
       </c>
       <c r="B2" t="n">
-        <v>90693</v>
+        <v>8425</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +715,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>516188</v>
+        <v>516064</v>
       </c>
       <c r="R2" t="n">
-        <v>6585531</v>
+        <v>6585564</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121690948</v>
+        <v>121692592</v>
       </c>
       <c r="B3" t="n">
-        <v>57726</v>
+        <v>8425</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,21 +821,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -838,9 +843,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516203</v>
+        <v>516205</v>
       </c>
       <c r="R3" t="n">
-        <v>6585542</v>
+        <v>6585468</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -879,22 +889,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:23</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:23</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,7 +924,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Indre Cepukaite</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -925,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121692590</v>
+        <v>121692584</v>
       </c>
       <c r="B4" t="n">
-        <v>8425</v>
+        <v>5193</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,21 +951,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -979,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516204</v>
+        <v>516080</v>
       </c>
       <c r="R4" t="n">
-        <v>6585475</v>
+        <v>6585588</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1014,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1024,7 +1034,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1055,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121692586</v>
+        <v>121692587</v>
       </c>
       <c r="B5" t="n">
-        <v>79234</v>
+        <v>8425</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1067,35 +1077,40 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1104,10 +1119,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516081</v>
+        <v>516166</v>
       </c>
       <c r="R5" t="n">
-        <v>6585590</v>
+        <v>6585544</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1139,7 +1154,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1149,7 +1164,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1305,10 +1320,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121692583</v>
+        <v>121692585</v>
       </c>
       <c r="B7" t="n">
-        <v>56569</v>
+        <v>5173</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1321,21 +1336,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1343,9 +1358,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1354,7 +1374,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516082</v>
+        <v>516079</v>
       </c>
       <c r="R7" t="n">
         <v>6585587</v>
@@ -1389,7 +1409,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1399,7 +1419,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1430,10 +1450,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121692585</v>
+        <v>121692581</v>
       </c>
       <c r="B8" t="n">
-        <v>5173</v>
+        <v>8425</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1446,21 +1466,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1484,13 +1504,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516079</v>
+        <v>516114</v>
       </c>
       <c r="R8" t="n">
-        <v>6585587</v>
+        <v>6585510</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1519,7 +1539,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1529,7 +1549,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1560,10 +1580,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121692584</v>
+        <v>121692583</v>
       </c>
       <c r="B9" t="n">
-        <v>5193</v>
+        <v>56569</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1576,21 +1596,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1598,14 +1618,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1614,13 +1629,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516080</v>
+        <v>516082</v>
       </c>
       <c r="R9" t="n">
-        <v>6585588</v>
+        <v>6585587</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1649,7 +1664,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1659,7 +1674,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1690,10 +1705,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121692592</v>
+        <v>121692589</v>
       </c>
       <c r="B10" t="n">
-        <v>8425</v>
+        <v>90728</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1702,25 +1717,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1730,12 +1745,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1744,10 +1754,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516205</v>
+        <v>516189</v>
       </c>
       <c r="R10" t="n">
-        <v>6585468</v>
+        <v>6585528</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1779,7 +1789,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1789,7 +1799,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1820,10 +1830,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121692587</v>
+        <v>121692588</v>
       </c>
       <c r="B11" t="n">
-        <v>8425</v>
+        <v>90693</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1836,36 +1846,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106554</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1874,10 +1879,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516166</v>
+        <v>516188</v>
       </c>
       <c r="R11" t="n">
-        <v>6585544</v>
+        <v>6585531</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1909,7 +1914,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1919,7 +1924,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1950,10 +1955,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121692581</v>
+        <v>121692586</v>
       </c>
       <c r="B12" t="n">
-        <v>8425</v>
+        <v>79234</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1962,25 +1967,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106554</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1990,12 +1995,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>516114</v>
+        <v>516081</v>
       </c>
       <c r="R12" t="n">
-        <v>6585510</v>
+        <v>6585590</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2080,10 +2080,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121692589</v>
+        <v>121692590</v>
       </c>
       <c r="B13" t="n">
-        <v>90728</v>
+        <v>8425</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2092,25 +2092,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2120,7 +2120,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2129,10 +2134,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516189</v>
+        <v>516204</v>
       </c>
       <c r="R13" t="n">
-        <v>6585528</v>
+        <v>6585475</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2164,7 +2169,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2174,7 +2179,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2205,10 +2210,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121692582</v>
+        <v>121690948</v>
       </c>
       <c r="B14" t="n">
-        <v>8425</v>
+        <v>57726</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2221,21 +2226,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106554</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2243,14 +2248,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516064</v>
+        <v>516203</v>
       </c>
       <c r="R14" t="n">
-        <v>6585564</v>
+        <v>6585542</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2289,22 +2289,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Indre Cepukaite</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">

--- a/artfynd/A 13453-2024 artfynd.xlsx
+++ b/artfynd/A 13453-2024 artfynd.xlsx
@@ -2080,10 +2080,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121692590</v>
+        <v>121690948</v>
       </c>
       <c r="B13" t="n">
-        <v>8425</v>
+        <v>57726</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2096,21 +2096,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106554</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2118,14 +2118,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2134,10 +2129,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516204</v>
+        <v>516203</v>
       </c>
       <c r="R13" t="n">
-        <v>6585475</v>
+        <v>6585542</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2164,22 +2159,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2199,7 +2194,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Indre Cepukaite</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2210,10 +2205,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121690948</v>
+        <v>121692590</v>
       </c>
       <c r="B14" t="n">
-        <v>57726</v>
+        <v>8425</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2226,21 +2221,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>106554</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2248,9 +2243,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516203</v>
+        <v>516204</v>
       </c>
       <c r="R14" t="n">
-        <v>6585542</v>
+        <v>6585475</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2289,22 +2289,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>07:23</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>07:23</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Indre Cepukaite</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">

--- a/artfynd/A 13453-2024 artfynd.xlsx
+++ b/artfynd/A 13453-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121692582</v>
+        <v>121690948</v>
       </c>
       <c r="B2" t="n">
-        <v>8425</v>
+        <v>57734</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,14 +713,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>516064</v>
+        <v>516203</v>
       </c>
       <c r="R2" t="n">
-        <v>6585564</v>
+        <v>6585542</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,22 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Indre Cepukaite</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -805,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121692592</v>
+        <v>121692581</v>
       </c>
       <c r="B3" t="n">
         <v>8425</v>
@@ -859,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516205</v>
+        <v>516114</v>
       </c>
       <c r="R3" t="n">
-        <v>6585468</v>
+        <v>6585510</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -894,7 +889,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +899,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,10 +930,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121692584</v>
+        <v>121692587</v>
       </c>
       <c r="B4" t="n">
-        <v>5193</v>
+        <v>8425</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,26 +946,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -989,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516080</v>
+        <v>516166</v>
       </c>
       <c r="R4" t="n">
-        <v>6585588</v>
+        <v>6585544</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1024,7 +1019,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,7 +1029,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,7 +1060,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121692587</v>
+        <v>121692590</v>
       </c>
       <c r="B5" t="n">
         <v>8425</v>
@@ -1100,7 +1095,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1119,10 +1114,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516166</v>
+        <v>516204</v>
       </c>
       <c r="R5" t="n">
-        <v>6585544</v>
+        <v>6585475</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1154,7 +1149,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1164,7 +1159,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1195,10 +1190,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121692901</v>
+        <v>121692583</v>
       </c>
       <c r="B6" t="n">
-        <v>58034</v>
+        <v>56577</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1211,21 +1206,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103044</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1235,7 +1230,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1244,13 +1239,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516180</v>
+        <v>516082</v>
       </c>
       <c r="R6" t="n">
-        <v>6585577</v>
+        <v>6585587</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1274,22 +1269,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1309,7 +1304,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ola Erlandsson</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1450,10 +1445,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121692581</v>
+        <v>121692901</v>
       </c>
       <c r="B8" t="n">
-        <v>8425</v>
+        <v>58042</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1466,21 +1461,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>103044</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1488,14 +1483,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1504,13 +1494,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516114</v>
+        <v>516180</v>
       </c>
       <c r="R8" t="n">
-        <v>6585510</v>
+        <v>6585577</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1534,22 +1524,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1569,7 +1559,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Ola Erlandsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1580,10 +1570,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121692583</v>
+        <v>121692592</v>
       </c>
       <c r="B9" t="n">
-        <v>56569</v>
+        <v>8425</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1596,21 +1586,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1618,9 +1608,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1629,13 +1624,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516082</v>
+        <v>516205</v>
       </c>
       <c r="R9" t="n">
-        <v>6585587</v>
+        <v>6585468</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1664,7 +1659,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1674,7 +1669,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1708,7 +1703,7 @@
         <v>121692589</v>
       </c>
       <c r="B10" t="n">
-        <v>90728</v>
+        <v>90742</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1830,10 +1825,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121692588</v>
+        <v>121692584</v>
       </c>
       <c r="B11" t="n">
-        <v>90693</v>
+        <v>5193</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1846,21 +1841,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>105930</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1870,7 +1865,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516188</v>
+        <v>516080</v>
       </c>
       <c r="R11" t="n">
-        <v>6585531</v>
+        <v>6585588</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1955,10 +1955,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121692586</v>
+        <v>121692582</v>
       </c>
       <c r="B12" t="n">
-        <v>79234</v>
+        <v>8425</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1967,25 +1967,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>106554</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1995,7 +1995,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2004,10 +2009,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>516081</v>
+        <v>516064</v>
       </c>
       <c r="R12" t="n">
-        <v>6585590</v>
+        <v>6585564</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -2039,7 +2044,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2049,7 +2054,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2080,10 +2085,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121690948</v>
+        <v>121692586</v>
       </c>
       <c r="B13" t="n">
-        <v>57726</v>
+        <v>79247</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2092,25 +2097,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2118,9 +2123,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2129,10 +2134,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516203</v>
+        <v>516081</v>
       </c>
       <c r="R13" t="n">
-        <v>6585542</v>
+        <v>6585590</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2159,22 +2164,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:23</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:23</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2194,7 +2199,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Indre Cepukaite</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2205,10 +2210,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121692590</v>
+        <v>121692588</v>
       </c>
       <c r="B14" t="n">
-        <v>8425</v>
+        <v>90707</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2221,21 +2226,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106554</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2245,12 +2250,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516204</v>
+        <v>516188</v>
       </c>
       <c r="R14" t="n">
-        <v>6585475</v>
+        <v>6585531</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 13453-2024 artfynd.xlsx
+++ b/artfynd/A 13453-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121690948</v>
+        <v>121692590</v>
       </c>
       <c r="B2" t="n">
-        <v>57734</v>
+        <v>8425</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,9 +713,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>516203</v>
+        <v>516204</v>
       </c>
       <c r="R2" t="n">
-        <v>6585542</v>
+        <v>6585475</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,22 +759,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:23</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:23</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Indre Cepukaite</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -930,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121692587</v>
+        <v>121692584</v>
       </c>
       <c r="B4" t="n">
-        <v>8425</v>
+        <v>5193</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,26 +951,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -984,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516166</v>
+        <v>516080</v>
       </c>
       <c r="R4" t="n">
-        <v>6585544</v>
+        <v>6585588</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1019,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1029,7 +1034,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1060,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121692590</v>
+        <v>121692901</v>
       </c>
       <c r="B5" t="n">
-        <v>8425</v>
+        <v>58042</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1076,21 +1081,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>103044</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1098,14 +1103,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1114,13 +1114,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516204</v>
+        <v>516180</v>
       </c>
       <c r="R5" t="n">
-        <v>6585475</v>
+        <v>6585577</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1144,22 +1144,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Ola Erlandsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1190,10 +1190,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121692583</v>
+        <v>121692592</v>
       </c>
       <c r="B6" t="n">
-        <v>56577</v>
+        <v>8425</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1228,9 +1228,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1239,13 +1244,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516082</v>
+        <v>516205</v>
       </c>
       <c r="R6" t="n">
-        <v>6585587</v>
+        <v>6585468</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1274,7 +1279,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1284,7 +1289,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1315,10 +1320,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121692585</v>
+        <v>121692583</v>
       </c>
       <c r="B7" t="n">
-        <v>5173</v>
+        <v>56577</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1331,21 +1336,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1353,14 +1358,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1369,7 +1369,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516079</v>
+        <v>516082</v>
       </c>
       <c r="R7" t="n">
         <v>6585587</v>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1445,10 +1445,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121692901</v>
+        <v>121692585</v>
       </c>
       <c r="B8" t="n">
-        <v>58042</v>
+        <v>5173</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1461,21 +1461,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103044</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1483,9 +1483,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1494,13 +1499,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516180</v>
+        <v>516079</v>
       </c>
       <c r="R8" t="n">
-        <v>6585577</v>
+        <v>6585587</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1524,22 +1529,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1559,7 +1564,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ola Erlandsson</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1570,10 +1575,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121692592</v>
+        <v>121692588</v>
       </c>
       <c r="B9" t="n">
-        <v>8425</v>
+        <v>90709</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1586,21 +1591,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1610,12 +1615,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1624,10 +1624,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516205</v>
+        <v>516188</v>
       </c>
       <c r="R9" t="n">
-        <v>6585468</v>
+        <v>6585531</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1700,10 +1700,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121692589</v>
+        <v>121692586</v>
       </c>
       <c r="B10" t="n">
-        <v>90742</v>
+        <v>79249</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516189</v>
+        <v>516081</v>
       </c>
       <c r="R10" t="n">
-        <v>6585528</v>
+        <v>6585590</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1825,10 +1825,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121692584</v>
+        <v>121690948</v>
       </c>
       <c r="B11" t="n">
-        <v>5193</v>
+        <v>57734</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1841,16 +1841,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105930</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1863,14 +1863,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1879,10 +1874,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516080</v>
+        <v>516203</v>
       </c>
       <c r="R11" t="n">
-        <v>6585588</v>
+        <v>6585542</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1909,22 +1904,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1944,7 +1939,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Indre Cepukaite</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1955,7 +1950,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121692582</v>
+        <v>121692587</v>
       </c>
       <c r="B12" t="n">
         <v>8425</v>
@@ -1990,7 +1985,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2009,10 +2004,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>516064</v>
+        <v>516166</v>
       </c>
       <c r="R12" t="n">
-        <v>6585564</v>
+        <v>6585544</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -2044,7 +2039,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2054,7 +2049,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2085,10 +2080,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121692586</v>
+        <v>121692582</v>
       </c>
       <c r="B13" t="n">
-        <v>79247</v>
+        <v>8425</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2097,25 +2092,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>106554</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2125,7 +2120,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516081</v>
+        <v>516064</v>
       </c>
       <c r="R13" t="n">
-        <v>6585590</v>
+        <v>6585564</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2210,10 +2210,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121692588</v>
+        <v>121692589</v>
       </c>
       <c r="B14" t="n">
-        <v>90707</v>
+        <v>90744</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2222,25 +2222,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516188</v>
+        <v>516189</v>
       </c>
       <c r="R14" t="n">
-        <v>6585531</v>
+        <v>6585528</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 13453-2024 artfynd.xlsx
+++ b/artfynd/A 13453-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121692590</v>
+        <v>121692582</v>
       </c>
       <c r="B2" t="n">
         <v>8425</v>
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>516204</v>
+        <v>516064</v>
       </c>
       <c r="R2" t="n">
-        <v>6585475</v>
+        <v>6585564</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121692581</v>
+        <v>121692584</v>
       </c>
       <c r="B3" t="n">
-        <v>8425</v>
+        <v>5193</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,21 +821,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516114</v>
+        <v>516080</v>
       </c>
       <c r="R3" t="n">
-        <v>6585510</v>
+        <v>6585588</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -894,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121692584</v>
+        <v>121692583</v>
       </c>
       <c r="B4" t="n">
-        <v>5193</v>
+        <v>56577</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,21 +951,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -973,14 +973,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -989,13 +984,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516080</v>
+        <v>516082</v>
       </c>
       <c r="R4" t="n">
-        <v>6585588</v>
+        <v>6585587</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1024,7 +1019,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,7 +1029,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,10 +1060,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121692901</v>
+        <v>121692588</v>
       </c>
       <c r="B5" t="n">
-        <v>58042</v>
+        <v>90710</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1081,21 +1076,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1103,9 +1098,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1114,13 +1109,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516180</v>
+        <v>516188</v>
       </c>
       <c r="R5" t="n">
-        <v>6585577</v>
+        <v>6585531</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1144,22 +1139,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1179,7 +1174,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ola Erlandsson</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1190,10 +1185,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121692592</v>
+        <v>121692589</v>
       </c>
       <c r="B6" t="n">
-        <v>8425</v>
+        <v>90745</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1202,25 +1197,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1230,12 +1225,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1244,10 +1234,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516205</v>
+        <v>516189</v>
       </c>
       <c r="R6" t="n">
-        <v>6585468</v>
+        <v>6585528</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1279,7 +1269,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1289,7 +1279,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1320,10 +1310,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121692583</v>
+        <v>121690948</v>
       </c>
       <c r="B7" t="n">
-        <v>56577</v>
+        <v>57734</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1336,21 +1326,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1360,7 +1350,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1369,13 +1359,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516082</v>
+        <v>516203</v>
       </c>
       <c r="R7" t="n">
-        <v>6585587</v>
+        <v>6585542</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1399,22 +1389,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1434,7 +1424,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Indre Cepukaite</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1575,10 +1565,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121692588</v>
+        <v>121692592</v>
       </c>
       <c r="B9" t="n">
-        <v>90709</v>
+        <v>8425</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1591,21 +1581,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1615,7 +1605,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1624,10 +1619,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516188</v>
+        <v>516205</v>
       </c>
       <c r="R9" t="n">
-        <v>6585531</v>
+        <v>6585468</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1659,7 +1654,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1669,7 +1664,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1703,7 +1698,7 @@
         <v>121692586</v>
       </c>
       <c r="B10" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1825,10 +1820,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121690948</v>
+        <v>121692587</v>
       </c>
       <c r="B11" t="n">
-        <v>57734</v>
+        <v>8425</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1841,31 +1836,36 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>106554</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516203</v>
+        <v>516166</v>
       </c>
       <c r="R11" t="n">
-        <v>6585542</v>
+        <v>6585544</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1904,22 +1904,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>07:23</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>07:23</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Indre Cepukaite</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1950,10 +1950,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121692587</v>
+        <v>121692901</v>
       </c>
       <c r="B12" t="n">
-        <v>8425</v>
+        <v>58042</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1966,36 +1966,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106554</v>
+        <v>103044</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>ex.</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2004,13 +1999,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>516166</v>
+        <v>516180</v>
       </c>
       <c r="R12" t="n">
-        <v>6585544</v>
+        <v>6585577</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2034,22 +2029,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2069,7 +2064,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Ola Erlandsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2080,7 +2075,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121692582</v>
+        <v>121692590</v>
       </c>
       <c r="B13" t="n">
         <v>8425</v>
@@ -2134,10 +2129,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516064</v>
+        <v>516204</v>
       </c>
       <c r="R13" t="n">
-        <v>6585564</v>
+        <v>6585475</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2169,7 +2164,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2179,7 +2174,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2210,10 +2205,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121692589</v>
+        <v>121692581</v>
       </c>
       <c r="B14" t="n">
-        <v>90744</v>
+        <v>8425</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2222,25 +2217,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2250,7 +2245,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516189</v>
+        <v>516114</v>
       </c>
       <c r="R14" t="n">
-        <v>6585528</v>
+        <v>6585510</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 13453-2024 artfynd.xlsx
+++ b/artfynd/A 13453-2024 artfynd.xlsx
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121692583</v>
+        <v>121692588</v>
       </c>
       <c r="B4" t="n">
-        <v>56577</v>
+        <v>90710</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,21 +951,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -973,9 +973,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516082</v>
+        <v>516188</v>
       </c>
       <c r="R4" t="n">
-        <v>6585587</v>
+        <v>6585531</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1060,10 +1060,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121692588</v>
+        <v>121692583</v>
       </c>
       <c r="B5" t="n">
-        <v>90710</v>
+        <v>56577</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1076,21 +1076,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1098,9 +1098,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1109,13 +1109,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516188</v>
+        <v>516082</v>
       </c>
       <c r="R5" t="n">
-        <v>6585531</v>
+        <v>6585587</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 13453-2024 artfynd.xlsx
+++ b/artfynd/A 13453-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121692582</v>
+        <v>121692584</v>
       </c>
       <c r="B2" t="n">
-        <v>8425</v>
+        <v>5193</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>516064</v>
+        <v>516080</v>
       </c>
       <c r="R2" t="n">
-        <v>6585564</v>
+        <v>6585588</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121692584</v>
+        <v>121692586</v>
       </c>
       <c r="B3" t="n">
-        <v>5193</v>
+        <v>79257</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,25 +817,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -845,12 +845,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516080</v>
+        <v>516081</v>
       </c>
       <c r="R3" t="n">
-        <v>6585588</v>
+        <v>6585590</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -894,7 +889,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +899,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,10 +930,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121692588</v>
+        <v>121692901</v>
       </c>
       <c r="B4" t="n">
-        <v>90710</v>
+        <v>58046</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,21 +946,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -973,9 +968,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -984,13 +979,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516188</v>
+        <v>516180</v>
       </c>
       <c r="R4" t="n">
-        <v>6585531</v>
+        <v>6585577</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1014,22 +1009,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-11</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,7 +1044,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Ola Erlandsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1060,10 +1055,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121692583</v>
+        <v>121692588</v>
       </c>
       <c r="B5" t="n">
-        <v>56577</v>
+        <v>90719</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1076,21 +1071,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1098,9 +1093,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1109,13 +1104,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516082</v>
+        <v>516188</v>
       </c>
       <c r="R5" t="n">
-        <v>6585587</v>
+        <v>6585531</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1144,7 +1139,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1154,7 +1149,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1185,10 +1180,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121692589</v>
+        <v>121692587</v>
       </c>
       <c r="B6" t="n">
-        <v>90745</v>
+        <v>8425</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1197,35 +1192,40 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1234,10 +1234,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516189</v>
+        <v>516166</v>
       </c>
       <c r="R6" t="n">
-        <v>6585528</v>
+        <v>6585544</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1310,10 +1310,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121690948</v>
+        <v>121692585</v>
       </c>
       <c r="B7" t="n">
-        <v>57734</v>
+        <v>5173</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1326,21 +1326,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1348,9 +1348,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1359,13 +1364,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516203</v>
+        <v>516079</v>
       </c>
       <c r="R7" t="n">
-        <v>6585542</v>
+        <v>6585587</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1389,22 +1394,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:23</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:23</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1424,7 +1429,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Indre Cepukaite</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1435,10 +1440,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121692585</v>
+        <v>121692581</v>
       </c>
       <c r="B8" t="n">
-        <v>5173</v>
+        <v>8425</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1451,21 +1456,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1489,13 +1494,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516079</v>
+        <v>516114</v>
       </c>
       <c r="R8" t="n">
-        <v>6585587</v>
+        <v>6585510</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1524,7 +1529,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1534,7 +1539,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1565,7 +1570,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121692592</v>
+        <v>121692582</v>
       </c>
       <c r="B9" t="n">
         <v>8425</v>
@@ -1619,10 +1624,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516205</v>
+        <v>516064</v>
       </c>
       <c r="R9" t="n">
-        <v>6585468</v>
+        <v>6585564</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1654,7 +1659,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1664,7 +1669,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1695,10 +1700,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121692586</v>
+        <v>121692590</v>
       </c>
       <c r="B10" t="n">
-        <v>79250</v>
+        <v>8425</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1707,25 +1712,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>106554</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1735,7 +1740,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1744,10 +1754,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516081</v>
+        <v>516204</v>
       </c>
       <c r="R10" t="n">
-        <v>6585590</v>
+        <v>6585475</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1779,7 +1789,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1789,7 +1799,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1820,10 +1830,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121692587</v>
+        <v>121692589</v>
       </c>
       <c r="B11" t="n">
-        <v>8425</v>
+        <v>90754</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1832,40 +1842,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1874,10 +1879,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516166</v>
+        <v>516189</v>
       </c>
       <c r="R11" t="n">
-        <v>6585544</v>
+        <v>6585528</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1909,7 +1914,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1919,7 +1924,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1950,10 +1955,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121692901</v>
+        <v>121690948</v>
       </c>
       <c r="B12" t="n">
-        <v>58042</v>
+        <v>57738</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1966,16 +1971,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1990,7 +1995,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1999,13 +2004,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>516180</v>
+        <v>516203</v>
       </c>
       <c r="R12" t="n">
-        <v>6585577</v>
+        <v>6585542</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2029,22 +2034,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2064,7 +2069,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ola Erlandsson</t>
+          <t>Indre Cepukaite</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2075,7 +2080,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121692590</v>
+        <v>121692592</v>
       </c>
       <c r="B13" t="n">
         <v>8425</v>
@@ -2129,10 +2134,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516204</v>
+        <v>516205</v>
       </c>
       <c r="R13" t="n">
-        <v>6585475</v>
+        <v>6585468</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2164,7 +2169,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2174,7 +2179,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2205,10 +2210,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121692581</v>
+        <v>121692583</v>
       </c>
       <c r="B14" t="n">
-        <v>8425</v>
+        <v>56581</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2221,21 +2226,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106554</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2243,14 +2248,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2259,13 +2259,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516114</v>
+        <v>516082</v>
       </c>
       <c r="R14" t="n">
-        <v>6585510</v>
+        <v>6585587</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
